--- a/4.1 Myrmidon Happy reef/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.158388658224559</v>
+        <v>1.188031824580763</v>
       </c>
       <c r="C3" t="n">
-        <v>2.123363204653171</v>
+        <v>2.145047584631359</v>
       </c>
       <c r="D3" t="n">
-        <v>15.68962422083363</v>
+        <v>15.68514745130227</v>
       </c>
       <c r="E3" t="n">
-        <v>18.97137608371136</v>
+        <v>19.01822686051439</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.226428684576243</v>
+        <v>1.269448868976338</v>
       </c>
       <c r="C4" t="n">
-        <v>2.077378142186251</v>
+        <v>2.098269733332622</v>
       </c>
       <c r="D4" t="n">
-        <v>15.46626680064045</v>
+        <v>15.3775560780847</v>
       </c>
       <c r="E4" t="n">
-        <v>18.77007362740294</v>
+        <v>18.74527468039366</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.45203430701216</v>
+        <v>1.512244893713617</v>
       </c>
       <c r="C5" t="n">
-        <v>2.043596203683118</v>
+        <v>2.070024851881442</v>
       </c>
       <c r="D5" t="n">
-        <v>14.99280915279037</v>
+        <v>14.88369771294039</v>
       </c>
       <c r="E5" t="n">
-        <v>18.48843966348565</v>
+        <v>18.46596745853545</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.878456422351762</v>
+        <v>1.967893638208646</v>
       </c>
       <c r="C6" t="n">
-        <v>2.047572281885317</v>
+        <v>2.077230880030613</v>
       </c>
       <c r="D6" t="n">
-        <v>14.92809234412642</v>
+        <v>14.7024376343053</v>
       </c>
       <c r="E6" t="n">
-        <v>18.8541210483635</v>
+        <v>18.74756215254456</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.588309099907419</v>
+        <v>2.705912657399144</v>
       </c>
       <c r="C7" t="n">
-        <v>2.056025129618883</v>
+        <v>2.078939121036003</v>
       </c>
       <c r="D7" t="n">
-        <v>14.55825816645961</v>
+        <v>14.29791831024744</v>
       </c>
       <c r="E7" t="n">
-        <v>19.20259239598591</v>
+        <v>19.08277008868259</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.655351044699191</v>
+        <v>3.824309824600068</v>
       </c>
       <c r="C8" t="n">
-        <v>2.082571587541716</v>
+        <v>2.091181514907961</v>
       </c>
       <c r="D8" t="n">
-        <v>14.36323398501098</v>
+        <v>14.03350420106265</v>
       </c>
       <c r="E8" t="n">
-        <v>20.10115661725189</v>
+        <v>19.94899554057068</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.168744583226776</v>
+        <v>5.404638921603202</v>
       </c>
       <c r="C9" t="n">
-        <v>2.105564118775177</v>
+        <v>2.113712624720426</v>
       </c>
       <c r="D9" t="n">
-        <v>14.39841000525414</v>
+        <v>13.93699840173519</v>
       </c>
       <c r="E9" t="n">
-        <v>21.6727187072561</v>
+        <v>21.45534994805882</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.2291483076066</v>
+        <v>7.592807292213704</v>
       </c>
       <c r="C10" t="n">
-        <v>2.131570615460674</v>
+        <v>2.13461403334384</v>
       </c>
       <c r="D10" t="n">
-        <v>14.28062973317566</v>
+        <v>13.73935295391622</v>
       </c>
       <c r="E10" t="n">
-        <v>23.64134865624293</v>
+        <v>23.46677427947376</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.955658031840844</v>
+        <v>10.50339471099422</v>
       </c>
       <c r="C11" t="n">
-        <v>2.172234605370578</v>
+        <v>2.161778992320349</v>
       </c>
       <c r="D11" t="n">
-        <v>13.97640575458366</v>
+        <v>13.3991773743947</v>
       </c>
       <c r="E11" t="n">
-        <v>26.10429839179508</v>
+        <v>26.06435107770927</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.43683721632961</v>
+        <v>14.20559475614007</v>
       </c>
       <c r="C12" t="n">
-        <v>2.207332085797401</v>
+        <v>2.18318109227293</v>
       </c>
       <c r="D12" t="n">
-        <v>13.59738241840509</v>
+        <v>13.00520202068045</v>
       </c>
       <c r="E12" t="n">
-        <v>29.2415517205321</v>
+        <v>29.39397786909345</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>17.65333561382219</v>
+        <v>18.68440632273036</v>
       </c>
       <c r="C13" t="n">
-        <v>2.224826829887079</v>
+        <v>2.193538530552734</v>
       </c>
       <c r="D13" t="n">
-        <v>13.57088504786747</v>
+        <v>12.86640253025404</v>
       </c>
       <c r="E13" t="n">
-        <v>33.44904749157674</v>
+        <v>33.74434738353713</v>
       </c>
     </row>
   </sheetData>

--- a/4.1 Myrmidon Happy reef/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.188031824580763</v>
+        <v>1.269636212934335</v>
       </c>
       <c r="C3" t="n">
-        <v>2.145047584631359</v>
+        <v>2.259101229126434</v>
       </c>
       <c r="D3" t="n">
-        <v>15.68514745130227</v>
+        <v>16.27200688718273</v>
       </c>
       <c r="E3" t="n">
-        <v>19.01822686051439</v>
+        <v>19.8007443292435</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.269448868976338</v>
+        <v>1.442707385580895</v>
       </c>
       <c r="C4" t="n">
-        <v>2.098269733332622</v>
+        <v>2.332268753083986</v>
       </c>
       <c r="D4" t="n">
-        <v>15.3775560780847</v>
+        <v>16.60385706726491</v>
       </c>
       <c r="E4" t="n">
-        <v>18.74527468039366</v>
+        <v>20.37883320592979</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.512244893713617</v>
+        <v>1.767936543017488</v>
       </c>
       <c r="C5" t="n">
-        <v>2.070024851881442</v>
+        <v>2.414563404239074</v>
       </c>
       <c r="D5" t="n">
-        <v>14.88369771294039</v>
+        <v>16.65553582893871</v>
       </c>
       <c r="E5" t="n">
-        <v>18.46596745853545</v>
+        <v>20.83803577619528</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.967893638208646</v>
+        <v>2.310190525618055</v>
       </c>
       <c r="C6" t="n">
-        <v>2.077230880030613</v>
+        <v>2.521989987419014</v>
       </c>
       <c r="D6" t="n">
-        <v>14.7024376343053</v>
+        <v>17.10064953228278</v>
       </c>
       <c r="E6" t="n">
-        <v>18.74756215254456</v>
+        <v>21.93283004531985</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.705912657399144</v>
+        <v>3.156596789035707</v>
       </c>
       <c r="C7" t="n">
-        <v>2.078939121036003</v>
+        <v>2.634225398284106</v>
       </c>
       <c r="D7" t="n">
-        <v>14.29791831024744</v>
+        <v>17.20826414650252</v>
       </c>
       <c r="E7" t="n">
-        <v>19.08277008868259</v>
+        <v>22.99908633382233</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.824309824600068</v>
+        <v>4.391011061283771</v>
       </c>
       <c r="C8" t="n">
-        <v>2.091181514907961</v>
+        <v>2.763337913510449</v>
       </c>
       <c r="D8" t="n">
-        <v>14.03350420106265</v>
+        <v>17.45702625511812</v>
       </c>
       <c r="E8" t="n">
-        <v>19.94899554057068</v>
+        <v>24.61137522991234</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.404638921603202</v>
+        <v>6.0672341165634</v>
       </c>
       <c r="C9" t="n">
-        <v>2.113712624720426</v>
+        <v>2.885413592457373</v>
       </c>
       <c r="D9" t="n">
-        <v>13.93699840173519</v>
+        <v>17.93759330450041</v>
       </c>
       <c r="E9" t="n">
-        <v>21.45534994805882</v>
+        <v>26.89024101352118</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.592807292213704</v>
+        <v>8.280437311795209</v>
       </c>
       <c r="C10" t="n">
-        <v>2.13461403334384</v>
+        <v>3.008531632988515</v>
       </c>
       <c r="D10" t="n">
-        <v>13.73935295391622</v>
+        <v>18.22580241853867</v>
       </c>
       <c r="E10" t="n">
-        <v>23.46677427947376</v>
+        <v>29.5147713633224</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10.50339471099422</v>
+        <v>11.09240689775376</v>
       </c>
       <c r="C11" t="n">
-        <v>2.161778992320349</v>
+        <v>3.130436387204429</v>
       </c>
       <c r="D11" t="n">
-        <v>13.3991773743947</v>
+        <v>18.25652086653874</v>
       </c>
       <c r="E11" t="n">
-        <v>26.06435107770927</v>
+        <v>32.47936415149693</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.20559475614007</v>
+        <v>14.51212739470072</v>
       </c>
       <c r="C12" t="n">
-        <v>2.18318109227293</v>
+        <v>3.242391278490921</v>
       </c>
       <c r="D12" t="n">
-        <v>13.00520202068045</v>
+        <v>18.15396545579509</v>
       </c>
       <c r="E12" t="n">
-        <v>29.39397786909345</v>
+        <v>35.90848412898673</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18.68440632273036</v>
+        <v>18.48849492624278</v>
       </c>
       <c r="C13" t="n">
-        <v>2.193538530552734</v>
+        <v>3.33416152985643</v>
       </c>
       <c r="D13" t="n">
-        <v>12.86640253025404</v>
+        <v>18.46293011173157</v>
       </c>
       <c r="E13" t="n">
-        <v>33.74434738353713</v>
+        <v>40.28558656783078</v>
       </c>
     </row>
   </sheetData>

--- a/4.1 Myrmidon Happy reef/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/4.1 Myrmidon Happy reef/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.269636212934335</v>
+        <v>1.237946124903378</v>
       </c>
       <c r="C3" t="n">
-        <v>2.259101229126434</v>
+        <v>2.233732981457118</v>
       </c>
       <c r="D3" t="n">
-        <v>16.27200688718273</v>
+        <v>16.2282203689871</v>
       </c>
       <c r="E3" t="n">
-        <v>19.8007443292435</v>
+        <v>19.6998994753476</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.442707385580895</v>
+        <v>1.379670946231219</v>
       </c>
       <c r="C4" t="n">
-        <v>2.332268753083986</v>
+        <v>2.2817449491727</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60385706726491</v>
+        <v>16.50361333511129</v>
       </c>
       <c r="E4" t="n">
-        <v>20.37883320592979</v>
+        <v>20.16502923051521</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.767936543017488</v>
+        <v>1.673530029840195</v>
       </c>
       <c r="C5" t="n">
-        <v>2.414563404239074</v>
+        <v>2.338863172833529</v>
       </c>
       <c r="D5" t="n">
-        <v>16.65553582893871</v>
+        <v>16.51650212418315</v>
       </c>
       <c r="E5" t="n">
-        <v>20.83803577619528</v>
+        <v>20.52889532685688</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.310190525618055</v>
+        <v>2.184445595931381</v>
       </c>
       <c r="C6" t="n">
-        <v>2.521989987419014</v>
+        <v>2.431926531751784</v>
       </c>
       <c r="D6" t="n">
-        <v>17.10064953228278</v>
+        <v>16.90848166921729</v>
       </c>
       <c r="E6" t="n">
-        <v>21.93283004531985</v>
+        <v>21.52485379690046</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.156596789035707</v>
+        <v>3.007906992139773</v>
       </c>
       <c r="C7" t="n">
-        <v>2.634225398284106</v>
+        <v>2.527815316725528</v>
       </c>
       <c r="D7" t="n">
-        <v>17.20826414650252</v>
+        <v>16.97884920025177</v>
       </c>
       <c r="E7" t="n">
-        <v>22.99908633382233</v>
+        <v>22.51457150911707</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.391011061283771</v>
+        <v>4.228042991815363</v>
       </c>
       <c r="C8" t="n">
-        <v>2.763337913510449</v>
+        <v>2.631469859490903</v>
       </c>
       <c r="D8" t="n">
-        <v>17.45702625511812</v>
+        <v>17.17787804633782</v>
       </c>
       <c r="E8" t="n">
-        <v>24.61137522991234</v>
+        <v>24.03739089764409</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.0672341165634</v>
+        <v>5.865412829372546</v>
       </c>
       <c r="C9" t="n">
-        <v>2.885413592457373</v>
+        <v>2.739415627523841</v>
       </c>
       <c r="D9" t="n">
-        <v>17.93759330450041</v>
+        <v>17.59713558502362</v>
       </c>
       <c r="E9" t="n">
-        <v>26.89024101352118</v>
+        <v>26.20196404192001</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.280437311795209</v>
+        <v>8.053243688227411</v>
       </c>
       <c r="C10" t="n">
-        <v>3.008531632988515</v>
+        <v>2.846738063115566</v>
       </c>
       <c r="D10" t="n">
-        <v>18.22580241853867</v>
+        <v>17.82791879967516</v>
       </c>
       <c r="E10" t="n">
-        <v>29.5147713633224</v>
+        <v>28.72790055101813</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11.09240689775376</v>
+        <v>10.83748030920501</v>
       </c>
       <c r="C11" t="n">
-        <v>3.130436387204429</v>
+        <v>2.955064116171131</v>
       </c>
       <c r="D11" t="n">
-        <v>18.25652086653874</v>
+        <v>17.82628674411065</v>
       </c>
       <c r="E11" t="n">
-        <v>32.47936415149693</v>
+        <v>31.61883116948679</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.51212739470072</v>
+        <v>14.24933126899397</v>
       </c>
       <c r="C12" t="n">
-        <v>3.242391278490921</v>
+        <v>3.057486422201928</v>
       </c>
       <c r="D12" t="n">
-        <v>18.15396545579509</v>
+        <v>17.72941440012652</v>
       </c>
       <c r="E12" t="n">
-        <v>35.90848412898673</v>
+        <v>35.03623209132242</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18.48849492624278</v>
+        <v>18.24816078941547</v>
       </c>
       <c r="C13" t="n">
-        <v>3.33416152985643</v>
+        <v>3.144411013528124</v>
       </c>
       <c r="D13" t="n">
-        <v>18.46293011173157</v>
+        <v>18.00410986790402</v>
       </c>
       <c r="E13" t="n">
-        <v>40.28558656783078</v>
+        <v>39.39668167084761</v>
       </c>
     </row>
   </sheetData>
